--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20231.xlsx
@@ -503,7 +503,7 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -512,10 +512,10 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>85.37</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -614,19 +614,22 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.93000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -640,16 +643,19 @@
         <v>33</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>33</v>
       </c>
-      <c r="E4">
-        <v>33</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -719,22 +725,22 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>85.70999999999999</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -751,16 +757,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20231.xlsx
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>82.93000000000001</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H3">
         <v>7.2</v>
@@ -766,7 +766,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20231.xlsx
@@ -483,7 +483,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -492,7 +492,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -594,7 +600,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -603,7 +609,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -705,7 +717,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -714,7 +726,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20231.xlsx
@@ -758,7 +758,7 @@
         <v>90.23999999999999</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -784,7 +784,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20231.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20231.xlsx
@@ -758,7 +758,7 @@
         <v>90.23999999999999</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -784,7 +784,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
